--- a/data/trans_dic/DCD-Clase-trans_dic.xlsx
+++ b/data/trans_dic/DCD-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante</t>
+          <t>Población con dolor crónico discapacitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,22</t>
+          <t>2,73; 6,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 8,4</t>
+          <t>3,58; 8,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,24</t>
+          <t>6,43; 11,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 14,81</t>
+          <t>7,56; 15,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 10,97</t>
+          <t>5,11; 11,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,67; 23,23</t>
+          <t>16,46; 22,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 9,32</t>
+          <t>5,35; 9,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,58</t>
+          <t>4,9; 8,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,74; 15,82</t>
+          <t>11,94; 16,11</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,86</t>
+          <t>3,34; 8,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,57</t>
+          <t>2,58; 7,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 13,19</t>
+          <t>7,87; 13,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 17,49</t>
+          <t>9,38; 16,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 14,78</t>
+          <t>7,55; 14,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,01; 26,06</t>
+          <t>19,5; 26,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 10,94</t>
+          <t>6,76; 11,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,9</t>
+          <t>5,7; 9,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,78; 18,39</t>
+          <t>13,77; 18,09</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 11,29</t>
+          <t>6,24; 11,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,59</t>
+          <t>4,97; 9,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 14,91</t>
+          <t>3,46; 15,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,35; 17,91</t>
+          <t>9,06; 18,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,35; 26,13</t>
+          <t>13,36; 24,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,05; 38,19</t>
+          <t>25,51; 37,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,18</t>
+          <t>7,88; 12,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 12,34</t>
+          <t>7,6; 12,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 20,09</t>
+          <t>6,41; 19,8</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,02</t>
+          <t>6,76; 10,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 9,23</t>
+          <t>5,92; 8,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,21; 18,6</t>
+          <t>14,15; 18,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,28; 16,33</t>
+          <t>11,35; 16,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,9</t>
+          <t>9,25; 13,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,82; 24,69</t>
+          <t>10,79; 24,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,04; 12,04</t>
+          <t>9,09; 11,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 10,42</t>
+          <t>7,84; 10,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,4; 20,01</t>
+          <t>12,15; 19,94</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,15</t>
+          <t>4,9; 9,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,9</t>
+          <t>7,86; 12,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,15; 22,28</t>
+          <t>15,09; 21,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,88; 23,86</t>
+          <t>17,96; 23,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 20,22</t>
+          <t>14,34; 20,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,28; 35,45</t>
+          <t>23,54; 35,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,19; 17,37</t>
+          <t>13,23; 17,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,24; 16,21</t>
+          <t>12,21; 15,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,75; 29,22</t>
+          <t>21,35; 29,2</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,62</t>
+          <t>1,39; 6,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,26; 21,01</t>
+          <t>16,11; 20,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,88; 15,27</t>
+          <t>11,01; 15,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,84; 30,77</t>
+          <t>24,95; 30,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,18; 17,17</t>
+          <t>12,88; 16,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,93; 12,35</t>
+          <t>8,88; 12,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,24; 24,19</t>
+          <t>19,33; 24,46</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 7,6</t>
+          <t>5,85; 7,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,65</t>
+          <t>5,88; 7,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,56; 13,64</t>
+          <t>9,74; 13,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,1; 17,71</t>
+          <t>15,09; 17,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,88; 14,27</t>
+          <t>11,85; 14,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,88; 26,89</t>
+          <t>20,02; 26,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,84; 12,43</t>
+          <t>10,82; 12,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,2; 10,69</t>
+          <t>9,13; 10,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,33; 20,16</t>
+          <t>16,25; 20,1</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante</t>
+          <t>Población con dolor crónico discapacitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12208; 31558</t>
+          <t>11932; 30139</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15660; 36059</t>
+          <t>15382; 35005</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32114; 56787</t>
+          <t>32479; 55786</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23738; 46568</t>
+          <t>23765; 47993</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17863; 38055</t>
+          <t>17751; 38691</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74580; 103931</t>
+          <t>73655; 102760</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40355; 70048</t>
+          <t>40178; 72288</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37898; 66623</t>
+          <t>38060; 66783</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>111814; 150723</t>
+          <t>113737; 153448</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13611; 32922</t>
+          <t>13968; 33840</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10525; 28545</t>
+          <t>9720; 28873</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33541; 59642</t>
+          <t>35595; 59270</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32697; 59128</t>
+          <t>31720; 57349</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27914; 55006</t>
+          <t>28101; 52246</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72729; 99682</t>
+          <t>74602; 101167</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49953; 82762</t>
+          <t>51180; 84205</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43543; 74226</t>
+          <t>42751; 74574</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>115041; 153481</t>
+          <t>114913; 151001</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39308; 71051</t>
+          <t>39288; 69291</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25931; 50036</t>
+          <t>25963; 49102</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21910; 99626</t>
+          <t>23104; 101985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24332; 46597</t>
+          <t>23556; 47246</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22178; 43401</t>
+          <t>22196; 41308</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43487; 63749</t>
+          <t>42580; 62294</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>70179; 108334</t>
+          <t>70084; 107023</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50877; 84931</t>
+          <t>52260; 84777</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>48343; 167789</t>
+          <t>53547; 165374</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78353; 116125</t>
+          <t>78340; 117479</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69112; 106061</t>
+          <t>68063; 103066</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>147071; 192495</t>
+          <t>146414; 192810</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86444; 125196</t>
+          <t>86985; 125670</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76025; 114806</t>
+          <t>76381; 114750</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96061; 241532</t>
+          <t>105533; 241080</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>174027; 231802</t>
+          <t>174973; 227649</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>155466; 205861</t>
+          <t>154812; 207544</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>249642; 402716</t>
+          <t>244469; 401302</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24506; 46733</t>
+          <t>25038; 50198</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47986; 80072</t>
+          <t>48760; 79760</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71949; 105859</t>
+          <t>71662; 104223</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136180; 181729</t>
+          <t>136780; 180668</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>106719; 149242</t>
+          <t>105871; 147852</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>187448; 298292</t>
+          <t>198052; 301446</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>167805; 221021</t>
+          <t>168326; 218843</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>166362; 220226</t>
+          <t>165873; 216278</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>286358; 384635</t>
+          <t>281038; 384430</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6677</t>
+          <t>0; 7840</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7666</t>
+          <t>0; 7723</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3422; 15914</t>
+          <t>3341; 16407</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>180352; 233047</t>
+          <t>178680; 231507</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>117769; 165178</t>
+          <t>119108; 165626</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>189105; 234273</t>
+          <t>189984; 231874</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>181334; 236276</t>
+          <t>177311; 232831</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>122333; 169072</t>
+          <t>121595; 166869</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>192720; 242320</t>
+          <t>193656; 245066</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>198444; 259923</t>
+          <t>200175; 260292</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>200076; 259002</t>
+          <t>199073; 260087</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>322815; 460494</t>
+          <t>328676; 458494</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>536008; 628597</t>
+          <t>535823; 625889</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>419630; 503882</t>
+          <t>418350; 502714</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>711316; 961918</t>
+          <t>716090; 960127</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>755491; 866932</t>
+          <t>754454; 864860</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>636400; 739175</t>
+          <t>631739; 736291</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1135342; 1401705</t>
+          <t>1129883; 1397776</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DCD-Clase-trans_dic.xlsx
+++ b/data/trans_dic/DCD-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,89</t>
+          <t>2,85; 6,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,16</t>
+          <t>3,55; 8,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 11,04</t>
+          <t>6,6; 11,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 15,26</t>
+          <t>7,7; 15,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,15</t>
+          <t>5,32; 11,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,46; 22,96</t>
+          <t>16,89; 23,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,62</t>
+          <t>5,36; 9,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 8,6</t>
+          <t>4,91; 8,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,94; 16,11</t>
+          <t>12,25; 16,27</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,08</t>
+          <t>3,19; 7,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,65</t>
+          <t>2,58; 7,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 13,11</t>
+          <t>7,45; 12,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 16,97</t>
+          <t>9,51; 17,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 14,03</t>
+          <t>7,56; 13,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,5; 26,44</t>
+          <t>20,3; 27,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,76; 11,13</t>
+          <t>6,67; 10,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 9,95</t>
+          <t>5,68; 9,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,77; 18,09</t>
+          <t>14,14; 18,53</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 11,01</t>
+          <t>6,26; 10,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,41</t>
+          <t>4,95; 9,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 15,26</t>
+          <t>11,09; 17,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,06; 18,16</t>
+          <t>9,43; 18,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,36; 24,87</t>
+          <t>13,38; 26,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,51; 37,32</t>
+          <t>26,91; 37,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 12,03</t>
+          <t>8,04; 12,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 12,32</t>
+          <t>7,59; 12,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,41; 19,8</t>
+          <t>16,41; 21,97</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,14</t>
+          <t>6,81; 10,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 8,97</t>
+          <t>5,94; 9,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,15; 18,63</t>
+          <t>13,99; 18,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 16,39</t>
+          <t>11,21; 16,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,25; 13,89</t>
+          <t>9,39; 13,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,79; 24,65</t>
+          <t>21,68; 26,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,09; 11,82</t>
+          <t>9,05; 12,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,51</t>
+          <t>7,81; 10,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,15; 19,94</t>
+          <t>17,89; 21,34</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 9,83</t>
+          <t>4,77; 9,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,86; 12,85</t>
+          <t>7,97; 12,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,09; 21,94</t>
+          <t>13,42; 19,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,96; 23,72</t>
+          <t>17,62; 23,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,34; 20,03</t>
+          <t>14,25; 20,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,54; 35,83</t>
+          <t>31,35; 36,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,23; 17,2</t>
+          <t>13,06; 17,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,21; 15,92</t>
+          <t>12,18; 16,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,35; 29,2</t>
+          <t>24,82; 29,07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,82</t>
+          <t>1,38; 6,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,11; 20,87</t>
+          <t>16,28; 21,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,01; 15,31</t>
+          <t>11,02; 15,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,95; 30,45</t>
+          <t>24,43; 30,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,88; 16,92</t>
+          <t>13,0; 17,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,88; 12,19</t>
+          <t>8,66; 12,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,33; 24,46</t>
+          <t>19,34; 24,33</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 7,61</t>
+          <t>5,84; 7,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,68</t>
+          <t>5,9; 7,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,74; 13,58</t>
+          <t>11,81; 14,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,09; 17,63</t>
+          <t>15,1; 17,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,85; 14,23</t>
+          <t>11,81; 14,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,02; 26,84</t>
+          <t>25,67; 28,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,82; 12,4</t>
+          <t>10,84; 12,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,13; 10,64</t>
+          <t>9,18; 10,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,25; 20,1</t>
+          <t>19,27; 20,97</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43361</t>
+          <t>47751</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88238</t>
+          <t>98792</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>131598</t>
+          <t>146543</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11932; 30139</t>
+          <t>12440; 29539</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15382; 35005</t>
+          <t>15229; 34576</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32479; 55786</t>
+          <t>36334; 61479</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23765; 47993</t>
+          <t>24200; 48826</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17751; 38691</t>
+          <t>18449; 38637</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73655; 102760</t>
+          <t>82477; 114632</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40178; 72288</t>
+          <t>40255; 69162</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38060; 66783</t>
+          <t>38090; 65614</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>113737; 153448</t>
+          <t>127276; 169005</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46556</t>
+          <t>47762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86301</t>
+          <t>99507</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>132857</t>
+          <t>147269</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13968; 33840</t>
+          <t>13360; 33449</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9720; 28873</t>
+          <t>9739; 28126</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35595; 59270</t>
+          <t>36019; 61806</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31720; 57349</t>
+          <t>32136; 59194</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28101; 52246</t>
+          <t>28156; 51243</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74602; 101167</t>
+          <t>85894; 116076</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51180; 84205</t>
+          <t>50493; 83164</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42751; 74574</t>
+          <t>42547; 73179</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>114913; 151001</t>
+          <t>128120; 167941</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60063</t>
+          <t>66506</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53660</t>
+          <t>60028</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>113723</t>
+          <t>126534</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39288; 69291</t>
+          <t>39432; 68868</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25963; 49102</t>
+          <t>25854; 49890</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23104; 101985</t>
+          <t>52318; 82896</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23556; 47246</t>
+          <t>24537; 47316</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22196; 41308</t>
+          <t>22234; 43457</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42580; 62294</t>
+          <t>50455; 70918</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>70084; 107023</t>
+          <t>71552; 108325</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>52260; 84777</t>
+          <t>52248; 85404</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53547; 165374</t>
+          <t>108172; 144832</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168599</t>
+          <t>180975</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>183735</t>
+          <t>207582</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>352334</t>
+          <t>388557</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78340; 117479</t>
+          <t>78872; 121008</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68063; 103066</t>
+          <t>68340; 105326</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>146414; 192810</t>
+          <t>158333; 206848</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86985; 125670</t>
+          <t>85936; 126059</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76381; 114750</t>
+          <t>77515; 113598</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>105533; 241080</t>
+          <t>186717; 229793</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>174973; 227649</t>
+          <t>174210; 231629</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>154812; 207544</t>
+          <t>154274; 208345</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>244469; 401302</t>
+          <t>356541; 425338</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87543</t>
+          <t>92544</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>260261</t>
+          <t>282701</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>347804</t>
+          <t>375245</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25038; 50198</t>
+          <t>24372; 48469</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48760; 79760</t>
+          <t>49480; 79554</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71662; 104223</t>
+          <t>76193; 111467</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136780; 180668</t>
+          <t>134162; 178359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>105871; 147852</t>
+          <t>105202; 148092</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>198052; 301446</t>
+          <t>260460; 306559</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>168326; 218843</t>
+          <t>166086; 218028</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>165873; 216278</t>
+          <t>165460; 218233</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>281038; 384430</t>
+          <t>347145; 406640</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>209947</t>
+          <t>228618</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>217778</t>
+          <t>236165</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 7840</t>
+          <t>0; 6707</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7723</t>
+          <t>0; 7674</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3341; 16407</t>
+          <t>3271; 14991</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>178680; 231507</t>
+          <t>180554; 234565</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>119108; 165626</t>
+          <t>119233; 165334</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>189984; 231874</t>
+          <t>206292; 253580</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>177311; 232831</t>
+          <t>178911; 236405</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>121595; 166869</t>
+          <t>118502; 168811</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>193656; 245066</t>
+          <t>209213; 263184</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>413953</t>
+          <t>443085</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>882142</t>
+          <t>977228</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1296094</t>
+          <t>1420313</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>200175; 260292</t>
+          <t>199671; 258744</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>199073; 260087</t>
+          <t>199737; 260646</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>328676; 458494</t>
+          <t>406705; 484150</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>535823; 625889</t>
+          <t>536077; 626170</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>418350; 502714</t>
+          <t>417236; 504078</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>716090; 960127</t>
+          <t>933177; 1023468</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>754454; 864860</t>
+          <t>755859; 868395</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>631739; 736291</t>
+          <t>635020; 734972</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1129883; 1397776</t>
+          <t>1363654; 1484379</t>
         </is>
       </c>
     </row>
